--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,619 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120334601</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>430432</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6817967</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120334602</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91839</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>430165</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6818060</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120334595</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>430059</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6818155</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120334598</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>430040</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6818237</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120334592</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>430015</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6818183</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120334593</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>430121</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6817928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334602</v>
+        <v>120334595</v>
       </c>
       <c r="B12" t="n">
-        <v>91839</v>
+        <v>79131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430165</v>
+        <v>430059</v>
       </c>
       <c r="R12" t="n">
-        <v>6818060</v>
+        <v>6818155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120334595</v>
+        <v>120334593</v>
       </c>
       <c r="B13" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430059</v>
+        <v>430121</v>
       </c>
       <c r="R13" t="n">
-        <v>6818155</v>
+        <v>6817928</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334598</v>
+        <v>120334592</v>
       </c>
       <c r="B14" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430040</v>
+        <v>430015</v>
       </c>
       <c r="R14" t="n">
-        <v>6818237</v>
+        <v>6818183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,6 +2118,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334592</v>
+        <v>120334602</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>91839</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2149,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430015</v>
+        <v>430165</v>
       </c>
       <c r="R15" t="n">
-        <v>6818183</v>
+        <v>6818060</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2221,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334593</v>
+        <v>120334598</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430121</v>
+        <v>430040</v>
       </c>
       <c r="R16" t="n">
-        <v>6817928</v>
+        <v>6818237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334601</v>
+        <v>120334592</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430432</v>
+        <v>430015</v>
       </c>
       <c r="R11" t="n">
-        <v>6817967</v>
+        <v>6818183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,6 +1812,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1830,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334595</v>
+        <v>120334601</v>
       </c>
       <c r="B12" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1847,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430059</v>
+        <v>430432</v>
       </c>
       <c r="R12" t="n">
-        <v>6818155</v>
+        <v>6817967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120334593</v>
+        <v>120334598</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1945,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430121</v>
+        <v>430040</v>
       </c>
       <c r="R13" t="n">
-        <v>6817928</v>
+        <v>6818237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334592</v>
+        <v>120334593</v>
       </c>
       <c r="B14" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430015</v>
+        <v>430121</v>
       </c>
       <c r="R14" t="n">
-        <v>6818183</v>
+        <v>6817928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2119,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334602</v>
+        <v>120334595</v>
       </c>
       <c r="B15" t="n">
-        <v>91839</v>
+        <v>79131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,25 +2149,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430165</v>
+        <v>430059</v>
       </c>
       <c r="R15" t="n">
-        <v>6818060</v>
+        <v>6818155</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334598</v>
+        <v>120334602</v>
       </c>
       <c r="B16" t="n">
-        <v>79131</v>
+        <v>91839</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430040</v>
+        <v>430165</v>
       </c>
       <c r="R16" t="n">
-        <v>6818237</v>
+        <v>6818060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334592</v>
+        <v>120334598</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430015</v>
+        <v>430040</v>
       </c>
       <c r="R11" t="n">
-        <v>6818183</v>
+        <v>6818237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1812,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334601</v>
+        <v>120334595</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>79131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1871,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430432</v>
+        <v>430059</v>
       </c>
       <c r="R12" t="n">
-        <v>6817967</v>
+        <v>6818155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120334598</v>
+        <v>120334602</v>
       </c>
       <c r="B13" t="n">
-        <v>79131</v>
+        <v>91839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430040</v>
+        <v>430165</v>
       </c>
       <c r="R13" t="n">
-        <v>6818237</v>
+        <v>6818060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334593</v>
+        <v>120334601</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430121</v>
+        <v>430432</v>
       </c>
       <c r="R14" t="n">
-        <v>6817928</v>
+        <v>6817967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334595</v>
+        <v>120334592</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430059</v>
+        <v>430015</v>
       </c>
       <c r="R15" t="n">
-        <v>6818155</v>
+        <v>6818183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,6 +2220,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334602</v>
+        <v>120334593</v>
       </c>
       <c r="B16" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430165</v>
+        <v>430121</v>
       </c>
       <c r="R16" t="n">
-        <v>6818060</v>
+        <v>6817928</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334598</v>
+        <v>120334592</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430040</v>
+        <v>430015</v>
       </c>
       <c r="R11" t="n">
-        <v>6818237</v>
+        <v>6818183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,6 +1812,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1830,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334595</v>
+        <v>120334593</v>
       </c>
       <c r="B12" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,25 +1843,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430059</v>
+        <v>430121</v>
       </c>
       <c r="R12" t="n">
-        <v>6818155</v>
+        <v>6817928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2034,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334601</v>
+        <v>120334595</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>79131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2051,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430432</v>
+        <v>430059</v>
       </c>
       <c r="R14" t="n">
-        <v>6817967</v>
+        <v>6818155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334592</v>
+        <v>120334598</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2153,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430015</v>
+        <v>430040</v>
       </c>
       <c r="R15" t="n">
-        <v>6818183</v>
+        <v>6818237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2221,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334593</v>
+        <v>120334601</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430121</v>
+        <v>430432</v>
       </c>
       <c r="R16" t="n">
-        <v>6817928</v>
+        <v>6817967</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334592</v>
+        <v>120334593</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,25 +1740,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430015</v>
+        <v>430121</v>
       </c>
       <c r="R11" t="n">
-        <v>6818183</v>
+        <v>6817928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1812,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334593</v>
+        <v>120334601</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1871,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430121</v>
+        <v>430432</v>
       </c>
       <c r="R12" t="n">
-        <v>6817928</v>
+        <v>6817967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120334602</v>
+        <v>120334595</v>
       </c>
       <c r="B13" t="n">
-        <v>91839</v>
+        <v>79131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430165</v>
+        <v>430059</v>
       </c>
       <c r="R13" t="n">
-        <v>6818060</v>
+        <v>6818155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334595</v>
+        <v>120334602</v>
       </c>
       <c r="B14" t="n">
-        <v>79131</v>
+        <v>91839</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430059</v>
+        <v>430165</v>
       </c>
       <c r="R14" t="n">
-        <v>6818155</v>
+        <v>6818060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334598</v>
+        <v>120334592</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430040</v>
+        <v>430015</v>
       </c>
       <c r="R15" t="n">
-        <v>6818237</v>
+        <v>6818183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,6 +2220,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334601</v>
+        <v>120334598</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>79131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430432</v>
+        <v>430040</v>
       </c>
       <c r="R16" t="n">
-        <v>6817967</v>
+        <v>6818237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334593</v>
+        <v>120334598</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,25 +1740,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430121</v>
+        <v>430040</v>
       </c>
       <c r="R11" t="n">
-        <v>6817928</v>
+        <v>6818237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334601</v>
+        <v>120334592</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430432</v>
+        <v>430015</v>
       </c>
       <c r="R12" t="n">
-        <v>6817967</v>
+        <v>6818183</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,6 +1914,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334602</v>
+        <v>120334593</v>
       </c>
       <c r="B14" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430165</v>
+        <v>430121</v>
       </c>
       <c r="R14" t="n">
-        <v>6818060</v>
+        <v>6817928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334592</v>
+        <v>120334601</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2153,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430015</v>
+        <v>430432</v>
       </c>
       <c r="R15" t="n">
-        <v>6818183</v>
+        <v>6817967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2221,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334598</v>
+        <v>120334602</v>
       </c>
       <c r="B16" t="n">
-        <v>79131</v>
+        <v>91839</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430040</v>
+        <v>430165</v>
       </c>
       <c r="R16" t="n">
-        <v>6818237</v>
+        <v>6818060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 17767-2024 artfynd.xlsx
+++ b/artfynd/A 17767-2024 artfynd.xlsx
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120334598</v>
+        <v>120334595</v>
       </c>
       <c r="B11" t="n">
         <v>79131</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430040</v>
+        <v>430059</v>
       </c>
       <c r="R11" t="n">
-        <v>6818237</v>
+        <v>6818155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120334592</v>
+        <v>120334593</v>
       </c>
       <c r="B12" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430015</v>
+        <v>430121</v>
       </c>
       <c r="R12" t="n">
-        <v>6818183</v>
+        <v>6817928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1914,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1933,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120334595</v>
+        <v>120334601</v>
       </c>
       <c r="B13" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430059</v>
+        <v>430432</v>
       </c>
       <c r="R13" t="n">
-        <v>6818155</v>
+        <v>6817967</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120334593</v>
+        <v>120334602</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430121</v>
+        <v>430165</v>
       </c>
       <c r="R14" t="n">
-        <v>6817928</v>
+        <v>6818060</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120334601</v>
+        <v>120334592</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430432</v>
+        <v>430015</v>
       </c>
       <c r="R15" t="n">
-        <v>6817967</v>
+        <v>6818183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,6 +2220,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120334602</v>
+        <v>120334598</v>
       </c>
       <c r="B16" t="n">
-        <v>91839</v>
+        <v>79131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430165</v>
+        <v>430040</v>
       </c>
       <c r="R16" t="n">
-        <v>6818060</v>
+        <v>6818237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
